--- a/sulamericana/datasets_sula/1_classificacao_por_jogo_oitavas_sula.xlsx
+++ b/sulamericana/datasets_sula/1_classificacao_por_jogo_oitavas_sula.xlsx
@@ -74,12 +74,12 @@
     <t>Jogo 3 (JG3)</t>
   </si>
   <si>
+    <t>Tatols Beants F.C</t>
+  </si>
+  <si>
     <t>dasdoresfc</t>
   </si>
   <si>
-    <t>Tatols Beants F.C</t>
-  </si>
-  <si>
     <t>Jogo 4 (JG4)</t>
   </si>
   <si>
@@ -101,28 +101,28 @@
     <t>Jogo 6 (JG6)</t>
   </si>
   <si>
+    <t>TORRESMO COM PINGA PRO26.1</t>
+  </si>
+  <si>
     <t>AZURRA82</t>
   </si>
   <si>
-    <t>TORRESMO COM PINGA PRO26.1</t>
-  </si>
-  <si>
     <t>Jogo 7 (JG7)</t>
   </si>
   <si>
+    <t>A Lenda Super Vasco F.c</t>
+  </si>
+  <si>
     <t>Grêmio imortal 37</t>
   </si>
   <si>
-    <t>A Lenda Super Vasco F.c</t>
-  </si>
-  <si>
     <t>Jogo 8 (JG8)</t>
   </si>
   <si>
+    <t>Mau Humor F.C.</t>
+  </si>
+  <si>
     <t>Super Vasco f.c</t>
-  </si>
-  <si>
-    <t>Mau Humor F.C.</t>
   </si>
 </sst>
 </file>
@@ -523,10 +523,10 @@
         <v>11</v>
       </c>
       <c r="C2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E2">
         <v>0</v>
@@ -535,13 +535,13 @@
         <v>0</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>104.97</v>
       </c>
       <c r="H2">
-        <v>0</v>
+        <v>97.56999999999999</v>
       </c>
       <c r="I2">
-        <v>0</v>
+        <v>7.400000000000006</v>
       </c>
       <c r="J2">
         <v>1</v>
@@ -564,16 +564,16 @@
         <v>0</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>97.56999999999999</v>
       </c>
       <c r="H3">
-        <v>0</v>
+        <v>104.97</v>
       </c>
       <c r="I3">
-        <v>0</v>
+        <v>-7.400000000000006</v>
       </c>
       <c r="J3">
         <v>2</v>
@@ -629,10 +629,10 @@
         <v>14</v>
       </c>
       <c r="C2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E2">
         <v>0</v>
@@ -641,13 +641,13 @@
         <v>0</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>114.97</v>
       </c>
       <c r="H2">
-        <v>0</v>
+        <v>104.38</v>
       </c>
       <c r="I2">
-        <v>0</v>
+        <v>10.59</v>
       </c>
       <c r="J2">
         <v>1</v>
@@ -670,16 +670,16 @@
         <v>0</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>104.38</v>
       </c>
       <c r="H3">
-        <v>0</v>
+        <v>114.97</v>
       </c>
       <c r="I3">
-        <v>0</v>
+        <v>-10.59</v>
       </c>
       <c r="J3">
         <v>2</v>
@@ -735,10 +735,10 @@
         <v>17</v>
       </c>
       <c r="C2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E2">
         <v>0</v>
@@ -747,13 +747,13 @@
         <v>0</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>115.35</v>
       </c>
       <c r="H2">
-        <v>0</v>
+        <v>111.47</v>
       </c>
       <c r="I2">
-        <v>0</v>
+        <v>3.879999999999995</v>
       </c>
       <c r="J2">
         <v>1</v>
@@ -776,16 +776,16 @@
         <v>0</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>111.47</v>
       </c>
       <c r="H3">
-        <v>0</v>
+        <v>115.35</v>
       </c>
       <c r="I3">
-        <v>0</v>
+        <v>-3.879999999999995</v>
       </c>
       <c r="J3">
         <v>2</v>
@@ -841,10 +841,10 @@
         <v>20</v>
       </c>
       <c r="C2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E2">
         <v>0</v>
@@ -853,13 +853,13 @@
         <v>0</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>101.87</v>
       </c>
       <c r="H2">
-        <v>0</v>
+        <v>95.37</v>
       </c>
       <c r="I2">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="J2">
         <v>1</v>
@@ -882,16 +882,16 @@
         <v>0</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>95.37</v>
       </c>
       <c r="H3">
-        <v>0</v>
+        <v>101.87</v>
       </c>
       <c r="I3">
-        <v>0</v>
+        <v>-6.5</v>
       </c>
       <c r="J3">
         <v>2</v>
@@ -947,10 +947,10 @@
         <v>23</v>
       </c>
       <c r="C2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E2">
         <v>0</v>
@@ -959,13 +959,13 @@
         <v>0</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>117.22</v>
       </c>
       <c r="H2">
-        <v>0</v>
+        <v>97.62</v>
       </c>
       <c r="I2">
-        <v>0</v>
+        <v>19.59999999999999</v>
       </c>
       <c r="J2">
         <v>1</v>
@@ -988,16 +988,16 @@
         <v>0</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>97.62</v>
       </c>
       <c r="H3">
-        <v>0</v>
+        <v>117.22</v>
       </c>
       <c r="I3">
-        <v>0</v>
+        <v>-19.59999999999999</v>
       </c>
       <c r="J3">
         <v>2</v>
@@ -1053,10 +1053,10 @@
         <v>26</v>
       </c>
       <c r="C2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E2">
         <v>0</v>
@@ -1065,13 +1065,13 @@
         <v>0</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>95.02</v>
       </c>
       <c r="H2">
-        <v>0</v>
+        <v>84.06999999999999</v>
       </c>
       <c r="I2">
-        <v>0</v>
+        <v>10.95</v>
       </c>
       <c r="J2">
         <v>1</v>
@@ -1094,16 +1094,16 @@
         <v>0</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>84.06999999999999</v>
       </c>
       <c r="H3">
-        <v>0</v>
+        <v>95.02</v>
       </c>
       <c r="I3">
-        <v>0</v>
+        <v>-10.95</v>
       </c>
       <c r="J3">
         <v>2</v>
@@ -1159,10 +1159,10 @@
         <v>29</v>
       </c>
       <c r="C2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E2">
         <v>0</v>
@@ -1171,13 +1171,13 @@
         <v>0</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>112.02</v>
       </c>
       <c r="H2">
-        <v>0</v>
+        <v>102.32</v>
       </c>
       <c r="I2">
-        <v>0</v>
+        <v>9.700000000000003</v>
       </c>
       <c r="J2">
         <v>1</v>
@@ -1200,16 +1200,16 @@
         <v>0</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>102.32</v>
       </c>
       <c r="H3">
-        <v>0</v>
+        <v>112.02</v>
       </c>
       <c r="I3">
-        <v>0</v>
+        <v>-9.700000000000003</v>
       </c>
       <c r="J3">
         <v>2</v>
@@ -1265,10 +1265,10 @@
         <v>32</v>
       </c>
       <c r="C2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E2">
         <v>0</v>
@@ -1277,13 +1277,13 @@
         <v>0</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>114.42</v>
       </c>
       <c r="H2">
-        <v>0</v>
+        <v>95.62</v>
       </c>
       <c r="I2">
-        <v>0</v>
+        <v>18.8</v>
       </c>
       <c r="J2">
         <v>1</v>
@@ -1306,16 +1306,16 @@
         <v>0</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>95.62</v>
       </c>
       <c r="H3">
-        <v>0</v>
+        <v>114.42</v>
       </c>
       <c r="I3">
-        <v>0</v>
+        <v>-18.8</v>
       </c>
       <c r="J3">
         <v>2</v>

--- a/sulamericana/datasets_sula/1_classificacao_por_jogo_oitavas_sula.xlsx
+++ b/sulamericana/datasets_sula/1_classificacao_por_jogo_oitavas_sula.xlsx
@@ -74,19 +74,19 @@
     <t>Jogo 3 (JG3)</t>
   </si>
   <si>
+    <t>dasdoresfc</t>
+  </si>
+  <si>
     <t>Tatols Beants F.C</t>
   </si>
   <si>
-    <t>dasdoresfc</t>
-  </si>
-  <si>
     <t>Jogo 4 (JG4)</t>
   </si>
   <si>
+    <t>JV5 Tricolor Gaúcho</t>
+  </si>
+  <si>
     <t>Grêmio imortal 36</t>
-  </si>
-  <si>
-    <t>JV5 Tricolor Gaúcho</t>
   </si>
   <si>
     <t>Jogo 5 (JG5)</t>
@@ -535,13 +535,13 @@
         <v>0</v>
       </c>
       <c r="G2">
-        <v>104.97</v>
+        <v>117.04</v>
       </c>
       <c r="H2">
-        <v>97.56999999999999</v>
+        <v>97.64</v>
       </c>
       <c r="I2">
-        <v>7.400000000000006</v>
+        <v>19.40000000000001</v>
       </c>
       <c r="J2">
         <v>1</v>
@@ -567,13 +567,13 @@
         <v>1</v>
       </c>
       <c r="G3">
-        <v>97.56999999999999</v>
+        <v>97.64</v>
       </c>
       <c r="H3">
-        <v>104.97</v>
+        <v>117.04</v>
       </c>
       <c r="I3">
-        <v>-7.400000000000006</v>
+        <v>-19.40000000000001</v>
       </c>
       <c r="J3">
         <v>2</v>
@@ -641,13 +641,13 @@
         <v>0</v>
       </c>
       <c r="G2">
-        <v>114.97</v>
+        <v>123.04</v>
       </c>
       <c r="H2">
-        <v>104.38</v>
+        <v>104.29</v>
       </c>
       <c r="I2">
-        <v>10.59</v>
+        <v>18.75</v>
       </c>
       <c r="J2">
         <v>1</v>
@@ -673,13 +673,13 @@
         <v>1</v>
       </c>
       <c r="G3">
-        <v>104.38</v>
+        <v>104.29</v>
       </c>
       <c r="H3">
-        <v>114.97</v>
+        <v>123.04</v>
       </c>
       <c r="I3">
-        <v>-10.59</v>
+        <v>-18.75</v>
       </c>
       <c r="J3">
         <v>2</v>
@@ -747,13 +747,13 @@
         <v>0</v>
       </c>
       <c r="G2">
-        <v>115.35</v>
+        <v>119.54</v>
       </c>
       <c r="H2">
-        <v>111.47</v>
+        <v>110.35</v>
       </c>
       <c r="I2">
-        <v>3.879999999999995</v>
+        <v>9.190000000000012</v>
       </c>
       <c r="J2">
         <v>1</v>
@@ -779,13 +779,13 @@
         <v>1</v>
       </c>
       <c r="G3">
-        <v>111.47</v>
+        <v>110.35</v>
       </c>
       <c r="H3">
-        <v>115.35</v>
+        <v>119.54</v>
       </c>
       <c r="I3">
-        <v>-3.879999999999995</v>
+        <v>-9.190000000000012</v>
       </c>
       <c r="J3">
         <v>2</v>
@@ -853,13 +853,13 @@
         <v>0</v>
       </c>
       <c r="G2">
-        <v>101.87</v>
+        <v>115.44</v>
       </c>
       <c r="H2">
-        <v>95.37</v>
+        <v>103.07</v>
       </c>
       <c r="I2">
-        <v>6.5</v>
+        <v>12.37</v>
       </c>
       <c r="J2">
         <v>1</v>
@@ -885,13 +885,13 @@
         <v>1</v>
       </c>
       <c r="G3">
-        <v>95.37</v>
+        <v>103.07</v>
       </c>
       <c r="H3">
-        <v>101.87</v>
+        <v>115.44</v>
       </c>
       <c r="I3">
-        <v>-6.5</v>
+        <v>-12.37</v>
       </c>
       <c r="J3">
         <v>2</v>
@@ -959,13 +959,13 @@
         <v>0</v>
       </c>
       <c r="G2">
-        <v>117.22</v>
+        <v>116.79</v>
       </c>
       <c r="H2">
-        <v>97.62</v>
+        <v>106.39</v>
       </c>
       <c r="I2">
-        <v>19.59999999999999</v>
+        <v>10.40000000000001</v>
       </c>
       <c r="J2">
         <v>1</v>
@@ -991,13 +991,13 @@
         <v>1</v>
       </c>
       <c r="G3">
-        <v>97.62</v>
+        <v>106.39</v>
       </c>
       <c r="H3">
-        <v>117.22</v>
+        <v>116.79</v>
       </c>
       <c r="I3">
-        <v>-19.59999999999999</v>
+        <v>-10.40000000000001</v>
       </c>
       <c r="J3">
         <v>2</v>
@@ -1065,13 +1065,13 @@
         <v>0</v>
       </c>
       <c r="G2">
-        <v>95.02</v>
+        <v>104.29</v>
       </c>
       <c r="H2">
-        <v>84.06999999999999</v>
+        <v>99.64</v>
       </c>
       <c r="I2">
-        <v>10.95</v>
+        <v>4.650000000000006</v>
       </c>
       <c r="J2">
         <v>1</v>
@@ -1097,13 +1097,13 @@
         <v>1</v>
       </c>
       <c r="G3">
-        <v>84.06999999999999</v>
+        <v>99.64</v>
       </c>
       <c r="H3">
-        <v>95.02</v>
+        <v>104.29</v>
       </c>
       <c r="I3">
-        <v>-10.95</v>
+        <v>-4.650000000000006</v>
       </c>
       <c r="J3">
         <v>2</v>
@@ -1171,13 +1171,13 @@
         <v>0</v>
       </c>
       <c r="G2">
-        <v>112.02</v>
+        <v>120.79</v>
       </c>
       <c r="H2">
-        <v>102.32</v>
+        <v>103.59</v>
       </c>
       <c r="I2">
-        <v>9.700000000000003</v>
+        <v>17.2</v>
       </c>
       <c r="J2">
         <v>1</v>
@@ -1203,13 +1203,13 @@
         <v>1</v>
       </c>
       <c r="G3">
-        <v>102.32</v>
+        <v>103.59</v>
       </c>
       <c r="H3">
-        <v>112.02</v>
+        <v>120.79</v>
       </c>
       <c r="I3">
-        <v>-9.700000000000003</v>
+        <v>-17.2</v>
       </c>
       <c r="J3">
         <v>2</v>
@@ -1277,13 +1277,13 @@
         <v>0</v>
       </c>
       <c r="G2">
-        <v>114.42</v>
+        <v>122.49</v>
       </c>
       <c r="H2">
-        <v>95.62</v>
+        <v>104.89</v>
       </c>
       <c r="I2">
-        <v>18.8</v>
+        <v>17.59999999999999</v>
       </c>
       <c r="J2">
         <v>1</v>
@@ -1309,13 +1309,13 @@
         <v>1</v>
       </c>
       <c r="G3">
-        <v>95.62</v>
+        <v>104.89</v>
       </c>
       <c r="H3">
-        <v>114.42</v>
+        <v>122.49</v>
       </c>
       <c r="I3">
-        <v>-18.8</v>
+        <v>-17.59999999999999</v>
       </c>
       <c r="J3">
         <v>2</v>

--- a/sulamericana/datasets_sula/1_classificacao_por_jogo_oitavas_sula.xlsx
+++ b/sulamericana/datasets_sula/1_classificacao_por_jogo_oitavas_sula.xlsx
@@ -535,13 +535,13 @@
         <v>0</v>
       </c>
       <c r="G2">
-        <v>117.04</v>
+        <v>117.0400390625</v>
       </c>
       <c r="H2">
-        <v>97.64</v>
+        <v>97.64013671875</v>
       </c>
       <c r="I2">
-        <v>19.40000000000001</v>
+        <v>19.39990234375</v>
       </c>
       <c r="J2">
         <v>1</v>
@@ -567,13 +567,13 @@
         <v>1</v>
       </c>
       <c r="G3">
-        <v>97.64</v>
+        <v>97.64013671875</v>
       </c>
       <c r="H3">
-        <v>117.04</v>
+        <v>117.0400390625</v>
       </c>
       <c r="I3">
-        <v>-19.40000000000001</v>
+        <v>-19.39990234375</v>
       </c>
       <c r="J3">
         <v>2</v>
@@ -641,10 +641,10 @@
         <v>0</v>
       </c>
       <c r="G2">
-        <v>123.04</v>
+        <v>123.0400390625</v>
       </c>
       <c r="H2">
-        <v>104.29</v>
+        <v>104.2900390625</v>
       </c>
       <c r="I2">
         <v>18.75</v>
@@ -673,10 +673,10 @@
         <v>1</v>
       </c>
       <c r="G3">
-        <v>104.29</v>
+        <v>104.2900390625</v>
       </c>
       <c r="H3">
-        <v>123.04</v>
+        <v>123.0400390625</v>
       </c>
       <c r="I3">
         <v>-18.75</v>
@@ -747,13 +747,13 @@
         <v>0</v>
       </c>
       <c r="G2">
-        <v>119.54</v>
+        <v>119.5400390625</v>
       </c>
       <c r="H2">
-        <v>110.35</v>
+        <v>110.35009765625</v>
       </c>
       <c r="I2">
-        <v>9.190000000000012</v>
+        <v>9.18994140625</v>
       </c>
       <c r="J2">
         <v>1</v>
@@ -779,13 +779,13 @@
         <v>1</v>
       </c>
       <c r="G3">
-        <v>110.35</v>
+        <v>110.35009765625</v>
       </c>
       <c r="H3">
-        <v>119.54</v>
+        <v>119.5400390625</v>
       </c>
       <c r="I3">
-        <v>-9.190000000000012</v>
+        <v>-9.18994140625</v>
       </c>
       <c r="J3">
         <v>2</v>
@@ -853,13 +853,13 @@
         <v>0</v>
       </c>
       <c r="G2">
-        <v>115.44</v>
+        <v>115.43994140625</v>
       </c>
       <c r="H2">
-        <v>103.07</v>
+        <v>103.06982421875</v>
       </c>
       <c r="I2">
-        <v>12.37</v>
+        <v>12.3701171875</v>
       </c>
       <c r="J2">
         <v>1</v>
@@ -885,13 +885,13 @@
         <v>1</v>
       </c>
       <c r="G3">
-        <v>103.07</v>
+        <v>103.06982421875</v>
       </c>
       <c r="H3">
-        <v>115.44</v>
+        <v>115.43994140625</v>
       </c>
       <c r="I3">
-        <v>-12.37</v>
+        <v>-12.3701171875</v>
       </c>
       <c r="J3">
         <v>2</v>
@@ -959,13 +959,13 @@
         <v>0</v>
       </c>
       <c r="G2">
-        <v>116.79</v>
+        <v>116.7900390625</v>
       </c>
       <c r="H2">
-        <v>106.39</v>
+        <v>106.39013671875</v>
       </c>
       <c r="I2">
-        <v>10.40000000000001</v>
+        <v>10.39990234375</v>
       </c>
       <c r="J2">
         <v>1</v>
@@ -991,13 +991,13 @@
         <v>1</v>
       </c>
       <c r="G3">
-        <v>106.39</v>
+        <v>106.39013671875</v>
       </c>
       <c r="H3">
-        <v>116.79</v>
+        <v>116.7900390625</v>
       </c>
       <c r="I3">
-        <v>-10.40000000000001</v>
+        <v>-10.39990234375</v>
       </c>
       <c r="J3">
         <v>2</v>
@@ -1065,13 +1065,13 @@
         <v>0</v>
       </c>
       <c r="G2">
-        <v>104.29</v>
+        <v>104.2900390625</v>
       </c>
       <c r="H2">
-        <v>99.64</v>
+        <v>99.64013671875</v>
       </c>
       <c r="I2">
-        <v>4.650000000000006</v>
+        <v>4.64990234375</v>
       </c>
       <c r="J2">
         <v>1</v>
@@ -1097,13 +1097,13 @@
         <v>1</v>
       </c>
       <c r="G3">
-        <v>99.64</v>
+        <v>99.64013671875</v>
       </c>
       <c r="H3">
-        <v>104.29</v>
+        <v>104.2900390625</v>
       </c>
       <c r="I3">
-        <v>-4.650000000000006</v>
+        <v>-4.64990234375</v>
       </c>
       <c r="J3">
         <v>2</v>
@@ -1171,13 +1171,13 @@
         <v>0</v>
       </c>
       <c r="G2">
-        <v>120.79</v>
+        <v>120.7900390625</v>
       </c>
       <c r="H2">
-        <v>103.59</v>
+        <v>103.58984375</v>
       </c>
       <c r="I2">
-        <v>17.2</v>
+        <v>17.2001953125</v>
       </c>
       <c r="J2">
         <v>1</v>
@@ -1203,13 +1203,13 @@
         <v>1</v>
       </c>
       <c r="G3">
-        <v>103.59</v>
+        <v>103.58984375</v>
       </c>
       <c r="H3">
-        <v>120.79</v>
+        <v>120.7900390625</v>
       </c>
       <c r="I3">
-        <v>-17.2</v>
+        <v>-17.2001953125</v>
       </c>
       <c r="J3">
         <v>2</v>
@@ -1277,13 +1277,13 @@
         <v>0</v>
       </c>
       <c r="G2">
-        <v>122.49</v>
+        <v>122.490234375</v>
       </c>
       <c r="H2">
-        <v>104.89</v>
+        <v>104.89013671875</v>
       </c>
       <c r="I2">
-        <v>17.59999999999999</v>
+        <v>17.60009765625</v>
       </c>
       <c r="J2">
         <v>1</v>
@@ -1309,13 +1309,13 @@
         <v>1</v>
       </c>
       <c r="G3">
-        <v>104.89</v>
+        <v>104.89013671875</v>
       </c>
       <c r="H3">
-        <v>122.49</v>
+        <v>122.490234375</v>
       </c>
       <c r="I3">
-        <v>-17.59999999999999</v>
+        <v>-17.60009765625</v>
       </c>
       <c r="J3">
         <v>2</v>

--- a/sulamericana/datasets_sula/1_classificacao_por_jogo_oitavas_sula.xlsx
+++ b/sulamericana/datasets_sula/1_classificacao_por_jogo_oitavas_sula.xlsx
@@ -101,19 +101,19 @@
     <t>Jogo 6 (JG6)</t>
   </si>
   <si>
+    <t>AZURRA82</t>
+  </si>
+  <si>
     <t>TORRESMO COM PINGA PRO26.1</t>
   </si>
   <si>
-    <t>AZURRA82</t>
-  </si>
-  <si>
     <t>Jogo 7 (JG7)</t>
   </si>
   <si>
+    <t>Grêmio imortal 37</t>
+  </si>
+  <si>
     <t>A Lenda Super Vasco F.c</t>
-  </si>
-  <si>
-    <t>Grêmio imortal 37</t>
   </si>
   <si>
     <t>Jogo 8 (JG8)</t>
@@ -523,10 +523,10 @@
         <v>11</v>
       </c>
       <c r="C2">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E2">
         <v>0</v>
@@ -535,13 +535,13 @@
         <v>0</v>
       </c>
       <c r="G2">
-        <v>117.0400390625</v>
+        <v>194.89013671875</v>
       </c>
       <c r="H2">
-        <v>97.64013671875</v>
+        <v>175.22021484375</v>
       </c>
       <c r="I2">
-        <v>19.39990234375</v>
+        <v>19.669921875</v>
       </c>
       <c r="J2">
         <v>1</v>
@@ -564,16 +564,16 @@
         <v>0</v>
       </c>
       <c r="F3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G3">
-        <v>97.64013671875</v>
+        <v>175.22021484375</v>
       </c>
       <c r="H3">
-        <v>117.0400390625</v>
+        <v>194.89013671875</v>
       </c>
       <c r="I3">
-        <v>-19.39990234375</v>
+        <v>-19.669921875</v>
       </c>
       <c r="J3">
         <v>2</v>
@@ -629,10 +629,10 @@
         <v>14</v>
       </c>
       <c r="C2">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E2">
         <v>0</v>
@@ -641,13 +641,13 @@
         <v>0</v>
       </c>
       <c r="G2">
-        <v>123.0400390625</v>
+        <v>197.7900390625</v>
       </c>
       <c r="H2">
-        <v>104.2900390625</v>
+        <v>158.6201171875</v>
       </c>
       <c r="I2">
-        <v>18.75</v>
+        <v>39.169921875</v>
       </c>
       <c r="J2">
         <v>1</v>
@@ -670,16 +670,16 @@
         <v>0</v>
       </c>
       <c r="F3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G3">
-        <v>104.2900390625</v>
+        <v>158.6201171875</v>
       </c>
       <c r="H3">
-        <v>123.0400390625</v>
+        <v>197.7900390625</v>
       </c>
       <c r="I3">
-        <v>-18.75</v>
+        <v>-39.169921875</v>
       </c>
       <c r="J3">
         <v>2</v>
@@ -735,10 +735,10 @@
         <v>17</v>
       </c>
       <c r="C2">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E2">
         <v>0</v>
@@ -747,13 +747,13 @@
         <v>0</v>
       </c>
       <c r="G2">
-        <v>119.5400390625</v>
+        <v>182.580078125</v>
       </c>
       <c r="H2">
-        <v>110.35009765625</v>
+        <v>161.43017578125</v>
       </c>
       <c r="I2">
-        <v>9.18994140625</v>
+        <v>21.14990234375</v>
       </c>
       <c r="J2">
         <v>1</v>
@@ -776,16 +776,16 @@
         <v>0</v>
       </c>
       <c r="F3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G3">
-        <v>110.35009765625</v>
+        <v>161.43017578125</v>
       </c>
       <c r="H3">
-        <v>119.5400390625</v>
+        <v>182.580078125</v>
       </c>
       <c r="I3">
-        <v>-9.18994140625</v>
+        <v>-21.14990234375</v>
       </c>
       <c r="J3">
         <v>2</v>
@@ -850,16 +850,16 @@
         <v>0</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G2">
-        <v>115.43994140625</v>
+        <v>173.169921875</v>
       </c>
       <c r="H2">
-        <v>103.06982421875</v>
+        <v>166.059814453125</v>
       </c>
       <c r="I2">
-        <v>12.3701171875</v>
+        <v>7.110107421875</v>
       </c>
       <c r="J2">
         <v>1</v>
@@ -873,10 +873,10 @@
         <v>21</v>
       </c>
       <c r="C3">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E3">
         <v>0</v>
@@ -885,13 +885,13 @@
         <v>1</v>
       </c>
       <c r="G3">
-        <v>103.06982421875</v>
+        <v>166.059814453125</v>
       </c>
       <c r="H3">
-        <v>115.43994140625</v>
+        <v>173.169921875</v>
       </c>
       <c r="I3">
-        <v>-12.3701171875</v>
+        <v>-7.110107421875</v>
       </c>
       <c r="J3">
         <v>2</v>
@@ -947,10 +947,10 @@
         <v>23</v>
       </c>
       <c r="C2">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E2">
         <v>0</v>
@@ -959,13 +959,13 @@
         <v>0</v>
       </c>
       <c r="G2">
-        <v>116.7900390625</v>
+        <v>193.27001953125</v>
       </c>
       <c r="H2">
-        <v>106.39013671875</v>
+        <v>160.170166015625</v>
       </c>
       <c r="I2">
-        <v>10.39990234375</v>
+        <v>33.099853515625</v>
       </c>
       <c r="J2">
         <v>1</v>
@@ -988,16 +988,16 @@
         <v>0</v>
       </c>
       <c r="F3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G3">
-        <v>106.39013671875</v>
+        <v>160.170166015625</v>
       </c>
       <c r="H3">
-        <v>116.7900390625</v>
+        <v>193.27001953125</v>
       </c>
       <c r="I3">
-        <v>-10.39990234375</v>
+        <v>-33.099853515625</v>
       </c>
       <c r="J3">
         <v>2</v>
@@ -1062,16 +1062,16 @@
         <v>0</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G2">
-        <v>104.2900390625</v>
+        <v>175.52001953125</v>
       </c>
       <c r="H2">
-        <v>99.64013671875</v>
+        <v>152.3701171875</v>
       </c>
       <c r="I2">
-        <v>4.64990234375</v>
+        <v>23.14990234375</v>
       </c>
       <c r="J2">
         <v>1</v>
@@ -1085,10 +1085,10 @@
         <v>27</v>
       </c>
       <c r="C3">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E3">
         <v>0</v>
@@ -1097,13 +1097,13 @@
         <v>1</v>
       </c>
       <c r="G3">
-        <v>99.64013671875</v>
+        <v>152.3701171875</v>
       </c>
       <c r="H3">
-        <v>104.2900390625</v>
+        <v>175.52001953125</v>
       </c>
       <c r="I3">
-        <v>-4.64990234375</v>
+        <v>-23.14990234375</v>
       </c>
       <c r="J3">
         <v>2</v>
@@ -1168,16 +1168,16 @@
         <v>0</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G2">
-        <v>120.7900390625</v>
+        <v>180.31982421875</v>
       </c>
       <c r="H2">
-        <v>103.58984375</v>
+        <v>162.739990234375</v>
       </c>
       <c r="I2">
-        <v>17.2001953125</v>
+        <v>17.579833984375</v>
       </c>
       <c r="J2">
         <v>1</v>
@@ -1191,10 +1191,10 @@
         <v>30</v>
       </c>
       <c r="C3">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E3">
         <v>0</v>
@@ -1203,13 +1203,13 @@
         <v>1</v>
       </c>
       <c r="G3">
-        <v>103.58984375</v>
+        <v>162.739990234375</v>
       </c>
       <c r="H3">
-        <v>120.7900390625</v>
+        <v>180.31982421875</v>
       </c>
       <c r="I3">
-        <v>-17.2001953125</v>
+        <v>-17.579833984375</v>
       </c>
       <c r="J3">
         <v>2</v>
@@ -1265,10 +1265,10 @@
         <v>32</v>
       </c>
       <c r="C2">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E2">
         <v>0</v>
@@ -1277,13 +1277,13 @@
         <v>0</v>
       </c>
       <c r="G2">
-        <v>122.490234375</v>
+        <v>175.97021484375</v>
       </c>
       <c r="H2">
-        <v>104.89013671875</v>
+        <v>155.14013671875</v>
       </c>
       <c r="I2">
-        <v>17.60009765625</v>
+        <v>20.830078125</v>
       </c>
       <c r="J2">
         <v>1</v>
@@ -1306,16 +1306,16 @@
         <v>0</v>
       </c>
       <c r="F3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G3">
-        <v>104.89013671875</v>
+        <v>155.14013671875</v>
       </c>
       <c r="H3">
-        <v>122.490234375</v>
+        <v>175.97021484375</v>
       </c>
       <c r="I3">
-        <v>-17.60009765625</v>
+        <v>-20.830078125</v>
       </c>
       <c r="J3">
         <v>2</v>
